--- a/artfynd/A 30447-2022 artfynd.xlsx
+++ b/artfynd/A 30447-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30447-2022 artfynd.xlsx
+++ b/artfynd/A 30447-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,10 +2221,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79006339</v>
+        <v>79006334</v>
       </c>
       <c r="B14" t="n">
-        <v>95511</v>
+        <v>95519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2237,36 +2237,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gravendal, skogsbilväg, Dlr</t>
@@ -2348,132 +2340,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
-        <is>
-          <t>Dalafloran inventeringsläger 2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>79006334</v>
-      </c>
-      <c r="B15" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Gravendal, skogsbilväg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>472709.1405717693</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6655688.269225976</v>
-      </c>
-      <c r="S15" t="n">
-        <v>50</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Säfsnäs</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grusig skogsbilväg och fuktigt dike.</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Ulf Swenson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Ulf Swenson, Lena Stigsdotter</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
         <is>
           <t>Dalafloran inventeringsläger 2019</t>
         </is>
